--- a/AAII_Financials/Quarterly/BAYRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAYRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>BAYRY</t>
   </si>
@@ -656,154 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -846,86 +849,89 @@
       <c r="P8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R8" s="3">
         <v>13291200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12191400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13948400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15883300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12053000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10533200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11483500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12584400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9969000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8828400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10968000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14503300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12549700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12041700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>27016000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14655800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12248900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10257500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10410100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10033500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9644600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9004000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9777000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>11362500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10356500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9693300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -968,86 +974,89 @@
       <c r="P9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R9" s="3">
         <v>5281000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4589700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6180400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5616000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3994900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4185900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4809700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4795700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3659500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7052500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4383300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5257100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5743700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4634100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10481700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5821900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6676300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4542300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3850700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3194100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3418700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2877900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3122500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3506200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3695200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3188100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1090,86 +1099,89 @@
       <c r="P10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R10" s="3">
         <v>8010200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7601600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7767900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10267400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8058100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6347200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6673900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7788700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6309600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1775800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6584700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9246200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6806000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7407500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>16534300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8833900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5572600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5715200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6559500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6839400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6225900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6126100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6654500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>7856300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6661400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>6505300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1212,8 +1224,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1256,86 +1269,89 @@
       <c r="P12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R12" s="3">
         <v>1787700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1703200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2097900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1577600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1097100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1684300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1733000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1222900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1287600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3493600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1273100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1470100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1633200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1569200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3083300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1575400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2008600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1292600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1391200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1141900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1384500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1210600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1230800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1284100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1461400</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1238400</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1456,8 +1472,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1500,8 +1519,8 @@
       <c r="P14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1578,8 +1597,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1622,8 +1644,8 @@
       <c r="P15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1700,8 +1722,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1741,8 +1766,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1785,86 +1811,89 @@
       <c r="P17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R17" s="3">
         <v>11705100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10895600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13764500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11313300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9862100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9962400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13896800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9437300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8458000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18583600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22732400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11681700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12095500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10561900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>23998600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12526600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17224200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5469300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8932200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7497100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8943400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>7446600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8135500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8513600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9668700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>8053500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1907,86 +1936,89 @@
       <c r="P18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R18" s="3">
         <v>1586100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1295800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>183900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4570000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2191000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>570800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2413300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3147100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1511100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9755200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11764400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2821600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>454100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1479800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3017500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2129200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4975300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4788200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1477900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2536400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>701200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1557300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1641500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2848800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>687900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1639800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2029,8 +2061,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -2073,86 +2106,89 @@
       <c r="P20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R20" s="3">
         <v>-622500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-646300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-753000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-531600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-568100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-361800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-104700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-355200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-141600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-301100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-736200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-441300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-219300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-884700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-356500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-851700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-752100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-354700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>142700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-289500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-452200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-414000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-347400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-262900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-273500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -2195,86 +2231,89 @@
       <c r="P21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R21" s="3">
         <v>3006000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1835000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2131600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5210200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1308500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1145800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1047400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3900500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1877100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>916500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10778200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3527300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1887700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2499000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5365600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3193900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-914400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5027400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1875400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3236900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1348600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1757000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1804200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3358300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2344100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1665600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2317,8 +2356,8 @@
       <c r="P22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2395,8 +2434,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -2439,86 +2481,89 @@
       <c r="P23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R23" s="3">
         <v>963600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>649500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-569100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4038400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1622900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>208900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2518000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2791900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1369400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9766600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-12065500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2085400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1260500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2132800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1772800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5827000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4036100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1123300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2679100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>411800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1105200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1227500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2501400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>424900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1366300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2561,86 +2606,89 @@
       <c r="P24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R24" s="3">
         <v>289100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-254600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>464400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>354500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>112000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-55000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>658400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>984400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1769600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1581800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>540800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>38000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>434100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>428200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1140300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>918200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>236100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>542400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>488100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>237900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>289500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>497700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>74000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2761,8 +2809,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,86 +2856,89 @@
       <c r="P26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R26" s="3">
         <v>674500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>596500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-314500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3574000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1268400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>96900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2463000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2133500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>385000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7997000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10483600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1544600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1222500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1698700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1344500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4686600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3117900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>887200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2136700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-76300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>867300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>938000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2003700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>351000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1123300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2927,86 +2981,89 @@
       <c r="P27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R27" s="3">
         <v>676700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>590100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-324300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3570700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1258600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>91500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2470400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2132500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>382000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7993900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10493500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1545700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-50200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1212700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1698700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1350500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4689000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3109000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>880600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2136700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-78500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>870700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>935700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1783000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>346300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1118600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3127,8 +3184,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3171,20 +3231,20 @@
       <c r="P29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>91</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -3196,61 +3256,64 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-74800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>5145900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>77500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>135500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1700900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>56300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>231800</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>134000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>47300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>70900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-8800</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>8800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>244600</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>3483800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>437600</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>662000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>185500</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3371,8 +3434,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3493,8 +3559,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -3537,86 +3606,89 @@
       <c r="P32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R32" s="3">
         <v>622500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>646300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>753000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>531600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>568100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>361800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>104700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>355200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>141600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>301100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>736200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>441300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>219300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>884700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>356500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>851700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>752100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>354700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-142700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>289500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>452200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>414000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>347400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>262900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>273500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -3659,86 +3731,89 @@
       <c r="P33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R33" s="3">
         <v>676700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>590100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-324300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3570700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1258600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>91500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2470400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2132500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>307200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2848000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10416000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1681200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1650700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1269100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1930500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1484500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4641700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3179900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>871800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2145500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>166100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4354400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1373300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2445000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>531700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1393300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3859,8 +3934,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -3903,213 +3981,219 @@
       <c r="P35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R35" s="3">
         <v>676700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>590100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-324300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3570700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1258600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>91500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2470400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2132500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>307200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2848000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10416000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1681200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1650700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1269100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1930500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1484500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4641700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3179900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>871800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2145500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>166100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4354400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1373300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2445000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>531700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1393300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4152,8 +4236,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4196,1106 +4281,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4900000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6604400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7832600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6918900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5351700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4339600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6409600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5151700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4165900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5097600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6529200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7213200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4891900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5273800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5727400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4712900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3712600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6276700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4947800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4647900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3585600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5665400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4180100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5259000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3434200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2584500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3718200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5402200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3932700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4859000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4793100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5371900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5469100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5854500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8505800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6232700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3111300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2610600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2229100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1446100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>906000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1074600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1391300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1578100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1101600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1479700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1962900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1918400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6574500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4528000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5173000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2636500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3437800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3390900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5768400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5093300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5203300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2613800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3623100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4203100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3289300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3840200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7919400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10869900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2792700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3118600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2715400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1401400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1022300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1019200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1379300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1773300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1709600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>8031900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3959500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>6806000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>8115400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>7819900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>7365700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>2541300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>18926100</v>
+      </c>
+      <c r="E43" s="3">
         <v>19152500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14289100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15586100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18940700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18095500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12618300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15424900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18248200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19197300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13841100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15086800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18957400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19680600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15220600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15937100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20004700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19339000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14399000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>14055700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16729100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16240900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12437600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13808200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17152400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>18828900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>17675800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>17387500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19478800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20154800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17129600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>15883000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>18145500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>12064800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11592400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11857200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>15914300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>18548500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>16263100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>15738400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>13676500</v>
+      </c>
+      <c r="E44" s="3">
         <v>13852200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14533300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14469100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14223100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13712700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13942400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14437900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14023400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14496700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15416200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14771400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15030600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14701200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15103200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13823200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>12372800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11792900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12265500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11462500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10712300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10674500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10932500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10848100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11048700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11297800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>12432900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>12733800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12082800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12574500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>13168000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12230100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>12023100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>7029400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>7349000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>7558800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>9490900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>10181600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>9869400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>9807200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E45" s="3">
         <v>18400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>595300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>726800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>223300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>3300</v>
       </c>
       <c r="Q45" s="3">
         <v>3300</v>
       </c>
       <c r="R45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S45" s="3">
         <v>1945300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1741000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1474500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>32300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>33900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>137800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>112700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1427200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1327300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3981200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1892800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>277500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>276800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>260300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4083500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3438900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2334900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2046500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>32900</v>
-      </c>
-      <c r="AO45" s="3">
-        <v>11700</v>
       </c>
       <c r="AP45" s="3">
         <v>11700</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>11700</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>38437100</v>
+      </c>
+      <c r="E46" s="3">
         <v>40702200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38641500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38579100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39640600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37648100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35660000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36951800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43013000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43334800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41512100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39720600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42333000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43049800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>41823000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41511800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>43034400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>41496900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>35317800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34401600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34350100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>36558900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>35582200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>40829900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>35728400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>37256900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>37869600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>40906100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>38409500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>38884900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>36746800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>35518500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>41430800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>36419600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>33741600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>34501200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>36635200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>39193500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>35739000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>29544800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>3442200</v>
+      </c>
+      <c r="E47" s="3">
         <v>3320700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3134900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3305200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3388100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3199300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3128700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3462000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3406200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3454500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3382300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2985800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3053500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3048700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4438200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4395200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4294700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4340000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4370000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3842400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3597200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3359500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2873500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3109500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3018500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3108400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3279300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4450400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4032700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4044400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3848000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4316300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4441400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5320900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>6777900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>6690400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2778000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2882900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2873500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2798400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>14575600</v>
+      </c>
+      <c r="E48" s="3">
         <v>14674300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14851500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14648600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14642400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14156900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13931000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14697700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14450900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14534500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14724200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14234800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14385400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14463300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15145300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15044400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14444500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13872800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13755100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12961600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12529900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12068900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11692500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11937900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12927300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13665500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14568100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16013100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16103700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>16666700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>15310300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14609200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14381600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>8048300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8564100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8308300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>14217900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>15359300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>15393300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>14555200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>56388700</v>
+      </c>
+      <c r="E49" s="3">
         <v>56326500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>57159800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56376900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>56735200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>54733000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>53968300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>56042800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>59874600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>60530800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>57611400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60377900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>65895200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>68020400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>70699200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75053500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>72848300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>71452700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>71945200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>69342700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>65596000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>64696300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>61681200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>62871800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>78750600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>83442700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>86195700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>92670500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86197200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>90551100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>88880700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>85576500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85283900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>28180200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>29648600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>30135500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>31985700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>34811700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>35072300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>35020600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5416,8 +5529,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5538,130 +5654,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>2436900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2239100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2125200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1907800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1772200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1726100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1636800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1576000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1341500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1292500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1288800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1238400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1323100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1290700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6208100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5577500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5518800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5311100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4965200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4963400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4729300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4309800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4670800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5300600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4484700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4199100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5384100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6040400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6190200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5782400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5125500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4535600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5569100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4813600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5514600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>6432400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7104400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>7589900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>7453700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>7917300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5782,130 +5904,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>122569400</v>
+      </c>
+      <c r="E54" s="3">
         <v>124459800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122743900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122269200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>123589000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118010200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>114763400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119279500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128424900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129335400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>128505600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>124091900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>132824200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>135867000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138313800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>141582500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>140140800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>136473500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>130353300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>125511600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120802400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120993400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>116500300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>124049800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>134909600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>141672700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>147296800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>160080500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>150933300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>155929500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>149911300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>144556200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>151106800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>82782600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>84246900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>86067900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>92721300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>99837200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>96531800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>89836400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5948,8 +6076,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5992,740 +6121,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>7303800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7592500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8314000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7486800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7091000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7119500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7783400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7317600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6564900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6902600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8241400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6879800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6517500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6810100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8356800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7077500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6634100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6344000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7363200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6016600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5409600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5292800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5663200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5668000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5561500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6019200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7501800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6978800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6333700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6835100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7142400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6154900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5456000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4329400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5754700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4407200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>5846700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>6679000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7524100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5788100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>8302300</v>
+      </c>
+      <c r="E58" s="3">
         <v>9458100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6746500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8128600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7893100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4717900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5007800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9837100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8934100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7549500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13032400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10873400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10569300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8706800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5761200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7152100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6400400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4760300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5160500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3922000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5048900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8546700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8573100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8042200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3613100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2547300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7378100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7853600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5007300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4355400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3867700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>10470500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1933600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2171100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3973000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>5651500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4928800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3992100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3185700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>21261300</v>
+      </c>
+      <c r="E59" s="3">
         <v>21528900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18790700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18359700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>19991800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18382000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14930100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15611200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17414600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17209000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15300100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15101600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17747800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19985900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21795400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23010300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22820700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20911200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19752300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19759000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20259600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19238000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>22462400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>22905400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>26261500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15569200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17052400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17562700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15766100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16841300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15856800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12639900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13753500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>8118600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7325500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8352100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9550400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>11366000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>10242700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>10601900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>36867400</v>
+      </c>
+      <c r="E60" s="3">
         <v>38579500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38258800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33975100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34975900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30219400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29974100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27936600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33816600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33045600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32560000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35013800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35138600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>37365300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38859000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>35849000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36606900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>33655600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31875800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30936100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29591200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>29579700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>36672400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>37146400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>39865100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25201500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27101400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>31919600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>29953500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>28683700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>27354600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22662600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>29680000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>14381600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15251200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16732200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>21048500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>22973800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>21758900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>19575600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>35603800</v>
+      </c>
+      <c r="E61" s="3">
         <v>35378800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37375800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38378500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37235500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37851300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36751200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40901200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40069600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>40982800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42197400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37162400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39909400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36474400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>37426900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42644400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>41414200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>39763100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39549100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39817300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>38795800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>38711800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>33114700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>36523700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37033100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>41564400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>43091400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>46258100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>43117400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>45397000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>44609500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>44700500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>46767100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>13475800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>14005800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>14110100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15896400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>17358300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>18992200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>19385500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>13244600</v>
+      </c>
+      <c r="E62" s="3">
         <v>13638900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12906000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11465400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11564300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10665800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10182200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11473300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11016800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11124200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11393800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11857500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11974900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11818800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18913400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18275700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20549900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22251200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22971000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21080300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>20088200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17229100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16118000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17709700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18884700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19828100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21730200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25476100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>25085600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>24434800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>23358700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21373400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>22817500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12779600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13632200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13426900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>15964800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>17415800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>18339600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>21778900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6846,8 +6994,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6968,8 +7119,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7090,130 +7244,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>88629000</v>
+      </c>
+      <c r="E66" s="3">
         <v>91066500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92142800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87421100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87769800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82794000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>81587100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85045700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90016100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90753000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>91943200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>88584900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>92295900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>91302700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>95368800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>96979900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>98772300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>95854300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>94556300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>92016800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>88650900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>85684900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>86056700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>91535500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>95959700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>86788300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>92133200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>103876700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>98357600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>98720000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>95525100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>88927000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>99344800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>40698500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>42956500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>44334300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>56088300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>60377300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>60926600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>62376300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7256,8 +7416,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7378,8 +7539,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7500,8 +7664,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7622,8 +7789,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7744,130 +7914,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" s="3">
         <v>7897100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J72" s="3">
         <v>10215300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N72" s="3">
         <v>13457500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>91</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R72" s="3">
         <v>19933500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>22150000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18762100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18077200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13273700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11121100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10170600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14100300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9721700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10950900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16285100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>31426200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>30909500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>30754600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>28136000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32358400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>29811400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>32618800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>28951000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>29155200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>28078900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>28522100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>23421500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>36975000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>33120200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>24975200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7988,8 +8164,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8110,8 +8289,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8232,130 +8414,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>33798700</v>
+      </c>
+      <c r="E76" s="3">
         <v>33258400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30465000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34703700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35666500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35070300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33034500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34083200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>38237400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38413000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>36395500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35330200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40336200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44398100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>42945000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44602700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41368500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40619100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35797000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>33494800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32151600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35308500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30443600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32514300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>38949900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>54884400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>55163600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>56203800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52575700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>57209500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>54386200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>55629200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>51761900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>42084100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>41290400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>41733500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>36633000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>39460000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>35605200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>27460100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8476,135 +8664,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -8647,86 +8841,89 @@
       <c r="P81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R81" s="3">
         <v>676700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>590100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-324300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3570700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1258600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>91500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2470400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2132500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>307200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2848000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10416000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1681200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1650700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1269100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1930500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1484500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4641700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3179900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>871800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2145500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>166100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4354400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1373300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2445000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>531700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1393300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8769,130 +8966,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E83" s="3">
         <v>550200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>416200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>448400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>429700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>421800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-5584200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>425500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>448700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>429200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-720300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>388300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>410800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>415500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2042400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1185500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2700700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1171800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-314400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>936900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1470600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1108600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>507700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10683100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1287300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1441900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1874900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1238500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3232700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1421100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5043900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>991300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>752100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>557800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>936900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>295100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>933500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>856900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1320500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>898000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9013,8 +9214,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9135,8 +9339,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9257,8 +9464,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9379,8 +9589,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9501,130 +9714,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>788300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2068500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4933700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1977000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1242500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1097100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5173400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2354500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2582200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2319600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6197600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2726500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>528400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3857000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3390400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2868200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2289400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-784500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3292400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3078900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2112800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2822500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>749000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2041500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2633500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-266500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3767200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2795400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3150400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1289500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3510800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2271700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2459500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>723600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2545800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3041700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2595200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>987200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3212700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3583600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9667,130 +9886,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-754000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-473900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-936900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-980900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-546100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-419400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1137800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-674800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-672900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-481200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-722900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-661600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-506300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-726000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-550000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-349000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1140000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-649000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-521600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-335800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-890700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-569800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-638200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-441500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1246800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-893000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1003500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-472500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1331900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-729900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-504000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-383200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1030000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-624900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-534100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-487100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>748900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-2657500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9911,8 +10134,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10033,130 +10259,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-807700</v>
+      </c>
+      <c r="E94" s="3">
         <v>322800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-608200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1251900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>180900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>174000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1339700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4191400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2789000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>326900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4293100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-146100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1197600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1740500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>74200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-452800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3015100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>805100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1071100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2745000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>472900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4027100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-193500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2968400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-459300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-675200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>40900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-292800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-549400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>92100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-675400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>7090900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-41641700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2259700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1917500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>194100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1321700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1333400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-5849100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2393400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10199,71 +10431,72 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>91</v>
+      <c r="D96" s="3">
+        <v>128000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3">
         <v>9400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>126800</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K96" s="3">
         <v>5600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>115700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N96" s="3">
         <v>16600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>4200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2574200</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R96" s="3">
         <v>-16600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-4300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-26000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -10271,58 +10504,61 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3001100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3071600</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2638500</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10443,8 +10679,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10565,8 +10804,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10687,370 +10929,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1687400</v>
+      </c>
+      <c r="E100" s="3">
         <v>608800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3394400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>856500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-566100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1341300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2183500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5636900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-741500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>730400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2711400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-169300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>296900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1805700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2371400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1448100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1973800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1166400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1949200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>692400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4870000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>115400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1350500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2975700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1228400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>40600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5219500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1243400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3415100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1397200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3752200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9482200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>39249100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-637900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2138500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-41500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-616000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>717200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>3413400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-993000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-218400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-85400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>39300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-93700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>51400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-197900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>59300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-193400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>53900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>110800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>146600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>59400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>115300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>143200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>67400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-78800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-64300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-33800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-76800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>24700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>27500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-59800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-424900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-129600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-51600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-72900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-41500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>10600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>5900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1652000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1072300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>914600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1572200</v>
       </c>
-      <c r="G102" s="3">
-        <v>636500</v>
-      </c>
       <c r="H102" s="3">
+        <v>638900</v>
+      </c>
+      <c r="I102" s="3">
         <v>-2349800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1689600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>815300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-896800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1275200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1004800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2470400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-406100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-344400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>892700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1026700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2584200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1330200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>268900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>998300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2286300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1387300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-873700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1984500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>912000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-977800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1430100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1260500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-789400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-942800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-179400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-357900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2303600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2273200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3121400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>616000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>381500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>782900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>207800</v>
       </c>
     </row>
